--- a/corona-server-side-asp.net/Excels/Sections/מבט על/מאומתים אתמול.xlsx
+++ b/corona-server-side-asp.net/Excels/Sections/מבט על/מאומתים אתמול.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>מחצות</t>
   </si>
@@ -34,6 +34,12 @@
   </si>
   <si>
     <t>group</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Since midnight</t>
   </si>
 </sst>
 </file>
@@ -373,37 +379,43 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
-      <c r="C2" s="2">
+      <c r="B2" s="2"/>
+      <c r="D2" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="2">
+      <c r="D3" s="2">
         <v>0</v>
       </c>
       <c r="G3" s="2"/>
       <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3">
+      <c r="D4" s="3">
         <v>4860823</v>
       </c>
     </row>

--- a/corona-server-side-asp.net/Excels/Sections/מבט על/מאומתים אתמול.xlsx
+++ b/corona-server-side-asp.net/Excels/Sections/מבט על/מאומתים אתמול.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>מחצות</t>
   </si>
@@ -40,6 +40,9 @@
   </si>
   <si>
     <t>Since midnight</t>
+  </si>
+  <si>
+    <t>keyEnglish</t>
   </si>
 </sst>
 </file>
@@ -379,6 +382,9 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
@@ -425,6 +431,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>